--- a/payment_forms/046_stripe_animal_shelter_donation_form--payment_forms.xlsx
+++ b/payment_forms/046_stripe_animal_shelter_donation_form--payment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'once',_'label':_'once'}</t>
+          <t>once</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Once', 'label': 'Once'}</t>
+          <t>Once</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'reoccurring',_'label':_'reoccurring'}</t>
+          <t>reoccurring</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Reoccurring', 'label': 'Reoccurring'}</t>
+          <t>Reoccurring</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'monthly',_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Monthly', 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'bi-weekly',_'label':_'bi-weekly'}</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Bi-Weekly', 'label': 'Bi-Weekly'}</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'weekly',_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Weekly', 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'never',_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Never', 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'1_month',_'label':_'1_month'}</t>
+          <t>1_month</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '1 month', 'label': '1 month'}</t>
+          <t>1 month</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'2_months',_'label':_'2_months'}</t>
+          <t>2_months</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '2 months', 'label': '2 months'}</t>
+          <t>2 months</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'3_months',_'label':_'3_months'}</t>
+          <t>3_months</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': '3 months', 'label': '3 months'}</t>
+          <t>3 months</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'4_months',_'label':_'4_months'}</t>
+          <t>4_months</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': '4 months', 'label': '4 months'}</t>
+          <t>4 months</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'opt_in',_'label':_'opt_in'}</t>
+          <t>opt_in</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Opt in', 'label': 'Opt in'}</t>
+          <t>Opt in</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'opt_out',_'label':_'opt_out'}</t>
+          <t>opt_out</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Opt Out', 'label': 'Opt Out'}</t>
+          <t>Opt Out</t>
         </is>
       </c>
     </row>
